--- a/sampleprojects/TaxReturn/excel/states/OH.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/OH.xlsx
@@ -71,7 +71,7 @@
     <t>OH tax = max(AGI - $0, 0) x 3.5%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 0.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.035</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 0.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.035</t>
   </si>
   <si>
     <t>X</t>

--- a/sampleprojects/TaxReturn/excel/states/OH.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/OH.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <si>
     <t>DT: OH Tax</t>
   </si>
@@ -131,7 +131,7 @@
     <t>result</t>
   </si>
   <si>
-    <t>(11 attributes)</t>
+    <t>(13 attributes)</t>
   </si>
   <si>
     <t>oh_bracket_1_limit</t>
@@ -158,6 +158,15 @@
     <t>OH tax rate for bracket 1 - 0% (2025)</t>
   </si>
   <si>
+    <t>oh_bracket_2_base</t>
+  </si>
+  <si>
+    <t>342.0</t>
+  </si>
+  <si>
+    <t>OH 2025 tax at the bottom of bracket 2: $342.00 plus 2.75% of Ohio taxable income over $26,050, as the 2025 IT 1040 booklet (tax.ohio.gov) and R.C. 5747.02 print it. Ohio printed figures are inconsistent: the over-$100,000 base $2,394.32 is $360.69 (the 2024 base) + 2.75% x $73,950, not $342.00 + 2.75% x $73,950 = $2,375.63. The printed $342.00 is used as published (#1317).</t>
+  </si>
+  <si>
     <t>oh_bracket_2_limit</t>
   </si>
   <si>
@@ -174,6 +183,15 @@
   </si>
   <si>
     <t>OH tax rate for bracket 2 - 2.75% (2025)</t>
+  </si>
+  <si>
+    <t>oh_bracket_3_base</t>
+  </si>
+  <si>
+    <t>2394.32</t>
+  </si>
+  <si>
+    <t>OH 2025 tax at the bottom of bracket 3: $2,394.32 plus 3.125% of Ohio taxable income over $100,000, as the 2025 IT 1040 booklet and R.C. 5747.02 print it. $2,394.32 is consistent only with the 2024 bracket-2 base $360.69, not the 2025 $342.00 (see oh_bracket_2_base); the inconsistency is Ohio own figures (#1317).</t>
   </si>
   <si>
     <t>oh_bracket_3_rate</t>
@@ -1729,7 +1747,7 @@
         <v>8</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>8</v>
@@ -1738,7 +1756,7 @@
         <v>42</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>8</v>
@@ -1753,6 +1771,88 @@
         <v>8</v>
       </c>
       <c r="M14" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="7" t="s">
         <v>8</v>
       </c>
     </row>

--- a/sampleprojects/TaxReturn/excel/states/OH.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/OH.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
   <si>
     <t>DT: OH Tax</t>
   </si>
@@ -131,7 +131,7 @@
     <t>result</t>
   </si>
   <si>
-    <t>(13 attributes)</t>
+    <t>(11 attributes)</t>
   </si>
   <si>
     <t>oh_bracket_1_limit</t>
@@ -158,15 +158,6 @@
     <t>OH tax rate for bracket 1 - 0% (2025)</t>
   </si>
   <si>
-    <t>oh_bracket_2_base</t>
-  </si>
-  <si>
-    <t>342.0</t>
-  </si>
-  <si>
-    <t>OH 2025 tax at the bottom of bracket 2: $342.00 plus 2.75% of Ohio taxable income over $26,050, as the 2025 IT 1040 booklet (tax.ohio.gov) and R.C. 5747.02 print it. Ohio printed figures are inconsistent: the over-$100,000 base $2,394.32 is $360.69 (the 2024 base) + 2.75% x $73,950, not $342.00 + 2.75% x $73,950 = $2,375.63. The printed $342.00 is used as published (#1317).</t>
-  </si>
-  <si>
     <t>oh_bracket_2_limit</t>
   </si>
   <si>
@@ -182,16 +173,7 @@
     <t>0.0275</t>
   </si>
   <si>
-    <t>OH tax rate for bracket 2 - 2.75% (2025)</t>
-  </si>
-  <si>
-    <t>oh_bracket_3_base</t>
-  </si>
-  <si>
-    <t>2394.32</t>
-  </si>
-  <si>
-    <t>OH 2025 tax at the bottom of bracket 3: $2,394.32 plus 3.125% of Ohio taxable income over $100,000, as the 2025 IT 1040 booklet and R.C. 5747.02 print it. $2,394.32 is consistent only with the 2024 bracket-2 base $360.69, not the 2025 $342.00 (see oh_bracket_2_base); the inconsistency is Ohio own figures (#1317).</t>
+    <t>OH tax rate for bracket 2 - 2.75% (2025): $342.00 plus 2.75% of Ohio taxable income over $26,050, as the 2025 IT 1040 booklet (tax.ohio.gov) and R.C. 5747.02 print it. The printed over-$100,000 base, $2,394.32, is $360.69 (the 2024 base) + 2.75% x $73,950, not $342.00 + 2.75% x $73,950 = $2,375.63; the inconsistency is Ohio own, and the printed figures are used as published (#1317).</t>
   </si>
   <si>
     <t>oh_bracket_3_rate</t>
@@ -200,7 +182,7 @@
     <t>0.03125</t>
   </si>
   <si>
-    <t>OH tax rate for bracket 3 (income &gt; $100,000) - 3.125% (2025)</t>
+    <t>OH tax rate for bracket 3 (income &gt; $100,000) - 3.125% (2025): $2,394.32 plus 3.125% over $100,000, as the 2025 IT 1040 booklet and R.C. 5747.02 print it; $2,394.32 is consistent only with the 2024 bracket-2 base $360.69 (see oh_bracket_2_rate) (#1317).</t>
   </si>
   <si>
     <t>oh_exemption_high</t>
@@ -1747,7 +1729,7 @@
         <v>8</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>8</v>
@@ -1756,7 +1738,7 @@
         <v>42</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>8</v>
@@ -1771,88 +1753,6 @@
         <v>8</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H15" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M15" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L16" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M16" s="7" t="s">
         <v>8</v>
       </c>
     </row>

--- a/sampleprojects/TaxReturn/excel/states/OH.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/OH.xlsx
@@ -173,7 +173,7 @@
     <t>0.0275</t>
   </si>
   <si>
-    <t>OH tax rate for bracket 2 - 2.75% (2025)</t>
+    <t>OH tax rate for bracket 2 - 2.75% (2025): $342.00 plus 2.75% of Ohio taxable income over $26,050, as the 2025 IT 1040 booklet (tax.ohio.gov) and R.C. 5747.02 print it. The printed over-$100,000 base, $2,394.32, is $360.69 (the 2024 base) + 2.75% x $73,950, not $342.00 + 2.75% x $73,950 = $2,375.63; the inconsistency is Ohio own, and the printed figures are used as published (#1317).</t>
   </si>
   <si>
     <t>oh_bracket_3_rate</t>
@@ -182,7 +182,7 @@
     <t>0.03125</t>
   </si>
   <si>
-    <t>OH tax rate for bracket 3 (income &gt; $100,000) - 3.125% (2025)</t>
+    <t>OH tax rate for bracket 3 (income &gt; $100,000) - 3.125% (2025): $2,394.32 plus 3.125% over $100,000, as the 2025 IT 1040 booklet and R.C. 5747.02 print it; $2,394.32 is consistent only with the 2024 bracket-2 base $360.69 (see oh_bracket_2_rate) (#1317).</t>
   </si>
   <si>
     <t>oh_exemption_high</t>

--- a/sampleprojects/TaxReturn/excel/states/OH.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/OH.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
   <si>
     <t>DT: OH Tax</t>
   </si>
@@ -44,7 +44,7 @@
     <t/>
   </si>
   <si>
-    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; add "  Ohio Tax Calculation (top marginal 3.5%)" to job.audit_trail</t>
+    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; add "  Ohio Tax Calculation (top marginal 3.5%)" to job.audit_trail; set result.oh_military_retirement_deduction = result.military_retirement_income; add "  OH Schedule of Adjustments line 34 uniformed services retirement income: $" + result.oh_military_retirement_deduction to job.audit_trail</t>
   </si>
   <si>
     <t>CONDITIONS: COMMENTS</t>
@@ -71,7 +71,7 @@
     <t>OH tax = max(AGI - $0, 0) x 3.5%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 0.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.035</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.oh_military_retirement_deduction) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.035</t>
   </si>
   <si>
     <t>X</t>
@@ -131,7 +131,7 @@
     <t>result</t>
   </si>
   <si>
-    <t>(11 attributes)</t>
+    <t>(12 attributes)</t>
   </si>
   <si>
     <t>oh_bracket_1_limit</t>
@@ -234,6 +234,15 @@
   </si>
   <si>
     <t>OH tax exemption threshold - first $26,050 is tax-free (2025)</t>
+  </si>
+  <si>
+    <t>oh_military_retirement_deduction</t>
+  </si>
+  <si>
+    <t>rw</t>
+  </si>
+  <si>
+    <t>Ohio Schedule of Adjustments line 34, uniformed services retirement income: military retired pay included in federal AGI is deducted in full (R.C. 5747.01(A)(23); 2025 IT 1040 booklet p. 24). Computed per return from result.military_retirement_income (#1330).</t>
   </si>
 </sst>
 </file>
@@ -1756,6 +1765,47 @@
         <v>8</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/sampleprojects/TaxReturn/excel/states/OH.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/OH.xlsx
@@ -44,7 +44,7 @@
     <t/>
   </si>
   <si>
-    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; add "  Ohio Tax Calculation (top marginal 3.5%)" to job.audit_trail; set result.oh_military_retirement_deduction = result.military_retirement_income; add "  OH Schedule of Adjustments line 34 uniformed services retirement income: $" + result.oh_military_retirement_deduction to job.audit_trail</t>
+    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; add "  Ohio Tax Calculation (top marginal 3.5%)" to job.audit_trail; set result.oh_military_retirement_deduction = 0.0; if result.state_calc_resident_status is equal to "full_year" then { set result.oh_military_retirement_deduction = result.military_retirement_income; } endif; add "  OH Schedule of Adjustments line 34 uniformed services retirement income: $" + result.oh_military_retirement_deduction to job.audit_trail</t>
   </si>
   <si>
     <t>CONDITIONS: COMMENTS</t>

--- a/sampleprojects/TaxReturn/excel/states/OH.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/OH.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
   <si>
     <t>DT: OH Tax</t>
   </si>
@@ -44,7 +44,7 @@
     <t/>
   </si>
   <si>
-    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; add "  Ohio Tax Calculation (top marginal 3.5%)" to job.audit_trail</t>
+    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; add "  Ohio Tax Calculation (top marginal 3.5%)" to job.audit_trail; set result.oh_military_retirement_deduction = 0.0; if result.state_calc_resident_status is equal to "full_year" then { set result.oh_military_retirement_deduction = result.military_retirement_income; } endif; add "  OH Schedule of Adjustments line 34 uniformed services retirement income: $" + result.oh_military_retirement_deduction to job.audit_trail</t>
   </si>
   <si>
     <t>CONDITIONS: COMMENTS</t>
@@ -71,7 +71,7 @@
     <t>OH tax = max(AGI - $0, 0) x 3.5%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 0.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.035</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.oh_military_retirement_deduction) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.035</t>
   </si>
   <si>
     <t>X</t>
@@ -131,7 +131,7 @@
     <t>result</t>
   </si>
   <si>
-    <t>(11 attributes)</t>
+    <t>(12 attributes)</t>
   </si>
   <si>
     <t>oh_bracket_1_limit</t>
@@ -234,6 +234,15 @@
   </si>
   <si>
     <t>OH tax exemption threshold - first $26,050 is tax-free (2025)</t>
+  </si>
+  <si>
+    <t>oh_military_retirement_deduction</t>
+  </si>
+  <si>
+    <t>rw</t>
+  </si>
+  <si>
+    <t>Ohio Schedule of Adjustments line 34, uniformed services retirement income: military retired pay included in federal AGI is deducted in full (R.C. 5747.01(A)(23); 2025 IT 1040 booklet p. 24). Computed per return from result.military_retirement_income (#1330).</t>
   </si>
 </sst>
 </file>
@@ -1756,6 +1765,47 @@
         <v>8</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>